--- a/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18DF55CD-FBBE-4D4E-A3E2-7170B0520B18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FE5620-66E7-479E-8B3F-233F30F7E073}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1529F84F-9452-4661-87B0-F432CC96F92C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58CDE495-432F-4340-B818-D2AF3E840E97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F894C7C-F227-4EFD-B04E-857C9C8CEF99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BA5EAAE-C471-4032-98EA-85D798998E57}"/>
 </file>